--- a/1_Data/Sui_2014_APP/Exp3/Codebook_Sui_2014_APP_Exp3_Clean.xlsx
+++ b/1_Data/Sui_2014_APP/Exp3/Codebook_Sui_2014_APP_Exp3_Clean.xlsx
@@ -1,34 +1,141 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+  <si>
+    <t xml:space="preserve">Variable_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Variable_description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Variable_value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Variable_category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subject</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Participant number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Numerical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Task</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Task type: the kind of shape-label matching task performed in the trial (default self-matching; other tasks e.g. facialExpression-matching, monetaryValue-matching, self-pseudoWords)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">self-matching</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Categorical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Block</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Block number in the experiment; each block may contain practice or experimental trials</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trial number within the block</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matching</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type of matching task for the trial; indicates whether the shape and label match or not</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matching;Nonmatching</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shape_Origin_Identity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Original identity associated with the shape stimulus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stranger;self;mother</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shape_English_Identity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">English translation of the shape's identity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stranger;Self;Mother</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shape_Standardized_Identity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standardized identity for the shape used across experiments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stranger;Self;Close</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RT_ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reaction time for the response, measured in milliseconds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RT_sec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reaction time for the response, measured in seconds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accuracy of the participant's response</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0;1</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
   <fonts count="1">
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +154,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
 </styleSheet>
 </file>
 
@@ -170,10 +209,6 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -199,15 +234,12 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -233,6 +265,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -408,279 +441,180 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Variable_name</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Variable_description</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Variable_value</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Variable_category</t>
-        </is>
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Subject</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Participant number</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Numerical</t>
-        </is>
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Block</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Block number in the experiment; each block may contain practice or experimental trials</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Numerical</t>
-        </is>
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Trial</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Trial number within the block</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Numerical</t>
-        </is>
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Task type: the kind of shape-label matching task performed in the trial (default self-matching; other tasks e.g. facialExpression-matching, monetaryValue-matching, self-pseudoWords)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>self-matching</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Categorical</t>
-        </is>
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Matching</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Type of matching task for the trial; indicates whether the shape and label match or not</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Matching;Nonmatching</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Categorical</t>
-        </is>
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Shape_Origin_Identity</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Original identity associated with the shape stimulus</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>stranger;self;mother</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Categorical</t>
-        </is>
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Shape_English_Identity</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>English translation of the shape's identity</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Stranger;Self;Mother</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Categorical</t>
-        </is>
+      <c r="A8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Shape_Standardized_Identity</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Standardized identity for the shape used across experiments</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Stranger;Self;Close</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Categorical</t>
-        </is>
+      <c r="A9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>RT_ms</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Reaction time for the response, measured in milliseconds</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Numerical</t>
-        </is>
+      <c r="A10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>RT_sec</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Reaction time for the response, measured in seconds</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Numerical</t>
-        </is>
+      <c r="A11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>ACC</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Accuracy of the participant's response</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>0;1</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Categorical</t>
-        </is>
+      <c r="A12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>